--- a/Lab_1/Лаб1.xlsx
+++ b/Lab_1/Лаб1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maksim\Desktop\УМФ\Lab_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artyo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A9A879-988F-4639-A34B-010A7705CC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9924CECE-B911-4C7C-B50D-D5F83394468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{D0F995C1-D0E6-4E56-86E8-1EC11FD3FC62}"/>
+    <workbookView xWindow="-28920" yWindow="5775" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{D0F995C1-D0E6-4E56-86E8-1EC11FD3FC62}"/>
   </bookViews>
   <sheets>
     <sheet name="Квадрат" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="19">
   <si>
     <t>u</t>
   </si>
@@ -93,6 +93,12 @@
   <si>
     <t>Сетка: Прямоугольник. Тип: Неравномерная</t>
   </si>
+  <si>
+    <t>u-u*</t>
+  </si>
+  <si>
+    <t>||u-u*||</t>
+  </si>
 </sst>
 </file>
 
@@ -127,7 +133,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -231,11 +237,101 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -268,6 +364,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -292,7 +391,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -667,33 +784,33 @@
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14"/>
-      <c r="I3" s="15" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="15"/>
+      <c r="I3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="M3" s="12" t="s">
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="M3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R3" s="13"/>
-      <c r="S3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="15"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
@@ -705,60 +822,60 @@
       <c r="AE3" s="2"/>
     </row>
     <row r="4" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="E4" s="12" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="15"/>
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="I4" s="12" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="15"/>
+      <c r="I4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="M4" s="12" t="s">
+      <c r="J4" s="14"/>
+      <c r="K4" s="15"/>
+      <c r="M4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N4" s="13"/>
-      <c r="O4" s="14"/>
-      <c r="Q4" s="12" t="s">
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
+      <c r="Q4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="13"/>
-      <c r="S4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="15"/>
     </row>
     <row r="5" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
       <c r="D5"/>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
-      <c r="I5" s="12" t="s">
+      <c r="F5" s="14"/>
+      <c r="G5" s="15"/>
+      <c r="I5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="14"/>
-      <c r="M5" s="12" t="s">
+      <c r="J5" s="14"/>
+      <c r="K5" s="15"/>
+      <c r="M5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="13"/>
-      <c r="O5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="15"/>
       <c r="P5"/>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="R5" s="13"/>
-      <c r="S5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="15"/>
     </row>
     <row r="6" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -1296,70 +1413,70 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-      <c r="E17" s="12" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="E17" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="I17" s="12" t="s">
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
+      <c r="I17" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="M17" s="12" t="s">
+      <c r="J17" s="14"/>
+      <c r="K17" s="15"/>
+      <c r="M17" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="E18" s="12" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="E18" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="I18" s="12" t="s">
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
+      <c r="I18" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="14"/>
-      <c r="M18" s="12" t="s">
+      <c r="J18" s="14"/>
+      <c r="K18" s="15"/>
+      <c r="M18" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="E19" s="12" t="s">
+      <c r="B19" s="14"/>
+      <c r="C19" s="15"/>
+      <c r="E19" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="I19" s="12" t="s">
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
+      <c r="I19" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14"/>
-      <c r="M19" s="12" t="s">
+      <c r="J19" s="14"/>
+      <c r="K19" s="15"/>
+      <c r="M19" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="15"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
@@ -1971,12 +2088,11 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="M18:O18"/>
     <mergeCell ref="M19:O19"/>
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="E18:G18"/>
@@ -1993,11 +2109,12 @@
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="E4:G4"/>
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2009,27 +2126,28 @@
   <dimension ref="A1:AI231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="20.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="21.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="22" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -2041,130 +2159,130 @@
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="12" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="14"/>
-      <c r="H3" s="12" t="s">
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
+      <c r="H3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="12" t="s">
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="14"/>
-      <c r="O3" s="15" t="s">
+      <c r="L3" s="14"/>
+      <c r="M3" s="15"/>
+      <c r="O3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="12" t="s">
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="13"/>
-      <c r="T3" s="14"/>
-      <c r="V3" s="12" t="s">
+      <c r="S3" s="14"/>
+      <c r="T3" s="15"/>
+      <c r="V3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="12" t="s">
+      <c r="W3" s="14"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="15"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="12" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
-      <c r="H4" s="12" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
+      <c r="H4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="17" t="s">
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
-      <c r="O4" s="12" t="s">
+      <c r="L4" s="19"/>
+      <c r="M4" s="20"/>
+      <c r="O4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="12" t="s">
+      <c r="P4" s="14"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="13"/>
-      <c r="T4" s="14"/>
-      <c r="V4" s="12" t="s">
+      <c r="S4" s="14"/>
+      <c r="T4" s="15"/>
+      <c r="V4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="W4" s="13"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="12" t="s">
+      <c r="W4" s="14"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="14"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="15"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="12" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-      <c r="H5" s="12" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+      <c r="H5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="12" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14"/>
-      <c r="O5" s="12" t="s">
+      <c r="L5" s="14"/>
+      <c r="M5" s="15"/>
+      <c r="O5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="12" t="s">
+      <c r="P5" s="14"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="14"/>
-      <c r="V5" s="12" t="s">
+      <c r="S5" s="14"/>
+      <c r="T5" s="15"/>
+      <c r="V5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="W5" s="13"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="12" t="s">
+      <c r="W5" s="14"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="15"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -5774,22 +5892,22 @@
       <c r="AF58" s="3"/>
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="H59" s="15" t="s">
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="H59" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="15"/>
-      <c r="M59" s="15"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
       <c r="X59" s="2"/>
       <c r="AB59" s="2"/>
       <c r="AC59" s="9"/>
@@ -5798,26 +5916,26 @@
       <c r="AF59" s="3"/>
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15" t="s">
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="H60" s="15" t="s">
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="H60" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15" t="s">
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="L60" s="15"/>
-      <c r="M60" s="15"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
       <c r="X60" s="2"/>
       <c r="AB60" s="2"/>
       <c r="AC60" s="9"/>
@@ -5826,26 +5944,26 @@
       <c r="AF60" s="3"/>
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15" t="s">
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="H61" s="15" t="s">
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="H61" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15" t="s">
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="L61" s="15"/>
-      <c r="M61" s="15"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
       <c r="X61" s="2"/>
       <c r="AB61" s="2"/>
       <c r="AC61" s="9"/>
@@ -5854,26 +5972,26 @@
       <c r="AF61" s="3"/>
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15" t="s">
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="H62" s="15" t="s">
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="H62" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15" t="s">
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L62" s="15"/>
-      <c r="M62" s="15"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
       <c r="X62" s="2"/>
       <c r="AB62" s="2"/>
       <c r="AC62" s="9"/>
@@ -5889,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>0</v>
@@ -5898,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>0</v>
@@ -5907,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>0</v>
@@ -5916,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="X63" s="2"/>
       <c r="AB63" s="2"/>
@@ -6412,7 +6530,7 @@
       <c r="B74" s="6">
         <v>0.24740395925452199</v>
       </c>
-      <c r="C74" s="20">
+      <c r="C74" s="12">
         <f t="shared" si="10"/>
         <v>1.4987571179958525E-6</v>
       </c>
@@ -6422,7 +6540,7 @@
       <c r="E74" s="6">
         <v>0.24740395925452199</v>
       </c>
-      <c r="F74" s="20">
+      <c r="F74" s="12">
         <f t="shared" si="11"/>
         <v>2.1081703422992648E-5</v>
       </c>
@@ -6432,7 +6550,7 @@
       <c r="I74" s="11">
         <v>0.24740395925452199</v>
       </c>
-      <c r="J74" s="20">
+      <c r="J74" s="12">
         <f t="shared" si="14"/>
         <v>4.0057480099608966E-7</v>
       </c>
@@ -6442,7 +6560,7 @@
       <c r="L74" s="11">
         <v>0.24740395925452199</v>
       </c>
-      <c r="M74" s="20">
+      <c r="M74" s="12">
         <f t="shared" si="13"/>
         <v>7.0691508410047899E-6</v>
       </c>
@@ -6754,7 +6872,7 @@
       <c r="B81" s="6">
         <v>0.36627252908604702</v>
       </c>
-      <c r="C81" s="20">
+      <c r="C81" s="12">
         <f t="shared" si="10"/>
         <v>2.4629600050007916E-6</v>
       </c>
@@ -6764,7 +6882,7 @@
       <c r="E81" s="6">
         <v>0.36627252908604702</v>
       </c>
-      <c r="F81" s="20">
+      <c r="F81" s="12">
         <f t="shared" si="11"/>
         <v>1.1043934269600042E-4</v>
       </c>
@@ -6774,7 +6892,7 @@
       <c r="I81" s="11">
         <v>0.36627252908604702</v>
       </c>
-      <c r="J81" s="20">
+      <c r="J81" s="12">
         <f t="shared" si="14"/>
         <v>6.6403057197295112E-7</v>
       </c>
@@ -6784,7 +6902,7 @@
       <c r="L81" s="11">
         <v>0.36627252908604702</v>
       </c>
-      <c r="M81" s="20">
+      <c r="M81" s="12">
         <f t="shared" si="13"/>
         <v>4.4011365965990201E-5</v>
       </c>
@@ -7121,7 +7239,7 @@
       <c r="E88" s="6">
         <v>0.47942553860420301</v>
       </c>
-      <c r="F88" s="20">
+      <c r="F88" s="12">
         <f t="shared" si="11"/>
         <v>5.3856296365900613E-4</v>
       </c>
@@ -7141,7 +7259,7 @@
       <c r="L88" s="11">
         <v>0.47942553860420301</v>
       </c>
-      <c r="M88" s="20">
+      <c r="M88" s="12">
         <f t="shared" si="13"/>
         <v>2.4779913433298217E-4</v>
       </c>
@@ -7366,7 +7484,7 @@
       <c r="B93" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="C93" s="20">
+      <c r="C93" s="12">
         <f t="shared" si="10"/>
         <v>3.1672685649741794E-6</v>
       </c>
@@ -7376,7 +7494,7 @@
       <c r="E93" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="F93" s="20">
+      <c r="F93" s="12">
         <f t="shared" si="11"/>
         <v>1.8623019014050168E-3</v>
       </c>
@@ -7386,7 +7504,7 @@
       <c r="I93" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="J93" s="20">
+      <c r="J93" s="12">
         <f t="shared" si="14"/>
         <v>8.6526451703594631E-7</v>
       </c>
@@ -7396,7 +7514,7 @@
       <c r="L93" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="M93" s="20">
+      <c r="M93" s="12">
         <f t="shared" si="13"/>
         <v>7.1424895092397911E-4</v>
       </c>
@@ -7417,7 +7535,7 @@
       <c r="B94" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="C94" s="20">
+      <c r="C94" s="12">
         <f t="shared" si="10"/>
         <v>3.938706521044999E-6</v>
       </c>
@@ -7427,7 +7545,7 @@
       <c r="E94" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="F94" s="20">
+      <c r="F94" s="12">
         <f t="shared" si="11"/>
         <v>2.3807267682829369E-3</v>
       </c>
@@ -7437,7 +7555,7 @@
       <c r="I94" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="J94" s="20">
+      <c r="J94" s="12">
         <f t="shared" si="14"/>
         <v>1.0829333659811979E-6</v>
       </c>
@@ -7447,7 +7565,7 @@
       <c r="L94" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="M94" s="20">
+      <c r="M94" s="12">
         <f t="shared" si="13"/>
         <v>9.6588730442104254E-4</v>
       </c>
@@ -7468,7 +7586,7 @@
       <c r="B95" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="C95" s="20">
+      <c r="C95" s="12">
         <f t="shared" si="10"/>
         <v>4.6286277309848245E-6</v>
       </c>
@@ -7478,7 +7596,7 @@
       <c r="E95" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="F95" s="20">
+      <c r="F95" s="12">
         <f t="shared" si="11"/>
         <v>2.5921243343909328E-3</v>
       </c>
@@ -7488,7 +7606,7 @@
       <c r="I95" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="J95" s="20">
+      <c r="J95" s="12">
         <f t="shared" si="14"/>
         <v>1.2220218059688648E-6</v>
       </c>
@@ -7498,7 +7616,7 @@
       <c r="L95" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="M95" s="20">
+      <c r="M95" s="12">
         <f t="shared" si="13"/>
         <v>1.046543523193999E-3</v>
       </c>
@@ -7519,7 +7637,7 @@
       <c r="B96" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="C96" s="20">
+      <c r="C96" s="12">
         <f t="shared" si="10"/>
         <v>3.9387065200457982E-6</v>
       </c>
@@ -7529,7 +7647,7 @@
       <c r="E96" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="F96" s="20">
+      <c r="F96" s="12">
         <f t="shared" si="11"/>
         <v>2.3807267682829369E-3</v>
       </c>
@@ -7539,7 +7657,7 @@
       <c r="I96" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="J96" s="20">
+      <c r="J96" s="12">
         <f t="shared" si="14"/>
         <v>1.0829333659811979E-6</v>
       </c>
@@ -7549,7 +7667,7 @@
       <c r="L96" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="M96" s="20">
+      <c r="M96" s="12">
         <f t="shared" si="13"/>
         <v>9.6588707089795278E-4</v>
       </c>
@@ -7561,7 +7679,7 @@
       <c r="B97" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="C97" s="20">
+      <c r="C97" s="12">
         <f t="shared" si="10"/>
         <v>3.1672685649741794E-6</v>
       </c>
@@ -7571,7 +7689,7 @@
       <c r="E97" s="6">
         <v>0.58509727294046199</v>
       </c>
-      <c r="F97" s="20">
+      <c r="F97" s="12">
         <f t="shared" si="11"/>
         <v>1.8623019014050168E-3</v>
       </c>
@@ -7581,7 +7699,7 @@
       <c r="I97" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="J97" s="20">
+      <c r="J97" s="12">
         <f t="shared" si="14"/>
         <v>8.6526451703594631E-7</v>
       </c>
@@ -7591,7 +7709,7 @@
       <c r="L97" s="11">
         <v>0.58509727294046199</v>
       </c>
-      <c r="M97" s="20">
+      <c r="M97" s="12">
         <f t="shared" si="13"/>
         <v>7.142486953359839E-4</v>
       </c>
@@ -7697,7 +7815,7 @@
       <c r="E100" s="6">
         <v>0.68163876002333401</v>
       </c>
-      <c r="F100" s="20">
+      <c r="F100" s="12">
         <f t="shared" si="11"/>
         <v>6.9426803750499699E-3</v>
       </c>
@@ -7717,7 +7835,7 @@
       <c r="L100" s="11">
         <v>0.68163876002333401</v>
       </c>
-      <c r="M100" s="20">
+      <c r="M100" s="12">
         <f t="shared" si="13"/>
         <v>2.729080106966042E-3</v>
       </c>
@@ -7739,7 +7857,7 @@
       <c r="E101" s="6">
         <v>0.68163876002333401</v>
       </c>
-      <c r="F101" s="20">
+      <c r="F101" s="12">
         <f t="shared" si="11"/>
         <v>7.4611052419280011E-3</v>
       </c>
@@ -7759,7 +7877,7 @@
       <c r="L101" s="11">
         <v>0.68163876002333401</v>
       </c>
-      <c r="M101" s="20">
+      <c r="M101" s="12">
         <f t="shared" si="13"/>
         <v>3.0692846345979907E-3</v>
       </c>
@@ -7781,7 +7899,7 @@
       <c r="E102" s="6">
         <v>0.68163876002333401</v>
       </c>
-      <c r="F102" s="20">
+      <c r="F102" s="12">
         <f t="shared" si="11"/>
         <v>7.6725028080349977E-3</v>
       </c>
@@ -7801,7 +7919,7 @@
       <c r="L102" s="11">
         <v>0.68163876002333401</v>
       </c>
-      <c r="M102" s="20">
+      <c r="M102" s="12">
         <f t="shared" si="13"/>
         <v>3.1482807409179969E-3</v>
       </c>
@@ -7823,7 +7941,7 @@
       <c r="E103" s="6">
         <v>0.68163876002333401</v>
       </c>
-      <c r="F103" s="20">
+      <c r="F103" s="12">
         <f t="shared" si="11"/>
         <v>7.4611052419280011E-3</v>
       </c>
@@ -7843,7 +7961,7 @@
       <c r="L103" s="11">
         <v>0.68163876002333401</v>
       </c>
-      <c r="M103" s="20">
+      <c r="M103" s="12">
         <f t="shared" si="13"/>
         <v>3.0692843638580047E-3</v>
       </c>
@@ -7865,7 +7983,7 @@
       <c r="E104" s="6">
         <v>0.68163876002333401</v>
       </c>
-      <c r="F104" s="20">
+      <c r="F104" s="12">
         <f t="shared" si="11"/>
         <v>6.9426803750499699E-3</v>
       </c>
@@ -7885,64 +8003,104 @@
       <c r="L104" s="11">
         <v>0.68163876002333401</v>
       </c>
-      <c r="M104" s="20">
+      <c r="M104" s="12">
         <f t="shared" si="13"/>
         <v>2.7290798038249742E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+    <row r="105" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="B105" s="6">
+      <c r="B105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="8">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="8">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H105" s="11">
+      <c r="H105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="I105" s="11">
+      <c r="I105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="J105" s="4">
+      <c r="J105" s="8">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K105" s="11">
+      <c r="K105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="L105" s="11">
+      <c r="L105" s="7">
         <v>0.68163876002333401</v>
       </c>
-      <c r="M105" s="4">
+      <c r="M105" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K106" s="3"/>
-      <c r="L106" s="9"/>
+      <c r="A106" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" s="23"/>
+      <c r="C106" s="23"/>
+      <c r="D106" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" s="23"/>
+      <c r="F106" s="24"/>
+      <c r="H106" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" s="17"/>
+      <c r="J106" s="17"/>
+      <c r="K106" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L106" s="17"/>
+      <c r="M106" s="17"/>
       <c r="P106"/>
       <c r="Q106"/>
       <c r="R106"/>
       <c r="S106"/>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K107" s="3"/>
-      <c r="L107" s="9"/>
+    <row r="107" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="25">
+        <f>SQRT(SUMSQ(C64:C104))</f>
+        <v>9.6005553779769681E-6</v>
+      </c>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="26">
+        <f>SQRT(SUMSQ(F64:F104))</f>
+        <v>1.7085050785220286E-2</v>
+      </c>
+      <c r="E107" s="26"/>
+      <c r="F107" s="27"/>
+      <c r="H107" s="17">
+        <f>SQRT(SUMSQ(J64:J104))</f>
+        <v>2.626862376178791E-6</v>
+      </c>
+      <c r="I107" s="17"/>
+      <c r="J107" s="17"/>
+      <c r="K107" s="17">
+        <f>SQRT(SUMSQ(M64:M104))</f>
+        <v>6.9060310392669751E-3</v>
+      </c>
+      <c r="L107" s="17"/>
+      <c r="M107" s="17"/>
       <c r="P107"/>
       <c r="Q107"/>
       <c r="R107"/>
@@ -7965,8 +8123,24 @@
       <c r="S109"/>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="K110" s="3"/>
-      <c r="L110" s="9"/>
+      <c r="A110" s="21">
+        <f>LOG(A107/H107,2)</f>
+        <v>1.86977724774486</v>
+      </c>
+      <c r="B110" s="21"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="21"/>
+      <c r="H110" s="21">
+        <f>LOG(D107/K107,2)</f>
+        <v>1.3068058126422484</v>
+      </c>
+      <c r="I110" s="21"/>
+      <c r="J110" s="21"/>
+      <c r="K110" s="21"/>
+      <c r="L110" s="21"/>
+      <c r="M110" s="21"/>
       <c r="P110"/>
       <c r="Q110"/>
       <c r="R110"/>
@@ -8941,21 +9115,29 @@
       <c r="S231"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="V3:X3"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="V5:X5"/>
-    <mergeCell ref="Y5:AA5"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="Y4:AA4"/>
+  <mergeCells count="48">
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="H107:J107"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="H110:M110"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="K60:M60"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="K61:M61"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="K4:M4"/>
@@ -8967,19 +9149,21 @@
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="K62:M62"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="D62:F62"/>
     <mergeCell ref="H59:M59"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="K60:M60"/>
-    <mergeCell ref="H61:J61"/>
-    <mergeCell ref="K61:M61"/>
+    <mergeCell ref="V5:X5"/>
+    <mergeCell ref="Y5:AA5"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="Y4:AA4"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="V3:X3"/>
+    <mergeCell ref="Y3:AA3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9003,95 +9187,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="15"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="15"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="13"/>
-      <c r="S1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="15"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="15"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="13"/>
-      <c r="K2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="15"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="15"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="13"/>
-      <c r="S2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="15"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="E3" s="12" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="15"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="15"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="14"/>
-      <c r="Q3" s="12" t="s">
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
+      <c r="Q3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="13"/>
-      <c r="S3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="15"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -9160,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f>ABS(E5-F5)</f>
+        <f t="shared" ref="G5:G20" si="0">ABS(E5-F5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="1"/>
@@ -9204,7 +9388,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" ref="C6:C8" si="0">ABS(A6-B6)</f>
+        <f t="shared" ref="C6:C8" si="1">ABS(A6-B6)</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
@@ -9214,7 +9398,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="4">
-        <f>ABS(E6-F6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" s="1"/>
@@ -9225,7 +9409,7 @@
         <v>4</v>
       </c>
       <c r="K6" s="4">
-        <f t="shared" ref="K6:K20" si="1">ABS(I6-J6)</f>
+        <f t="shared" ref="K6:K20" si="2">ABS(I6-J6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="1"/>
@@ -9236,7 +9420,7 @@
         <v>101.62962962962899</v>
       </c>
       <c r="O6" s="4">
-        <f t="shared" ref="O6:O20" si="2">ABS(M6-N6)</f>
+        <f t="shared" ref="O6:O20" si="3">ABS(M6-N6)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="11">
@@ -9246,7 +9430,7 @@
         <v>16</v>
       </c>
       <c r="S6" s="4">
-        <f t="shared" ref="S6:S20" si="3">ABS(Q6-R6)</f>
+        <f t="shared" ref="S6:S20" si="4">ABS(Q6-R6)</f>
         <v>0</v>
       </c>
     </row>
@@ -9258,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E7" s="11">
@@ -9268,7 +9452,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="4">
-        <f>ABS(E7-F7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7" s="1"/>
@@ -9279,7 +9463,7 @@
         <v>36</v>
       </c>
       <c r="K7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L7" s="1"/>
@@ -9290,7 +9474,7 @@
         <v>813.03703703703695</v>
       </c>
       <c r="O7" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q7" s="11">
@@ -9300,7 +9484,7 @@
         <v>1296</v>
       </c>
       <c r="S7" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9312,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E8" s="11">
@@ -9322,7 +9506,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="4">
-        <f>ABS(E8-F8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8" s="1"/>
@@ -9333,7 +9517,7 @@
         <v>196</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L8" s="1"/>
@@ -9344,7 +9528,7 @@
         <v>2744</v>
       </c>
       <c r="O8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q8" s="11">
@@ -9354,7 +9538,7 @@
         <v>38416</v>
       </c>
       <c r="S8" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9376,7 +9560,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="4">
-        <f>ABS(E9-F9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" s="1"/>
@@ -9387,7 +9571,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L9" s="1"/>
@@ -9398,7 +9582,7 @@
         <v>101.62962962962899</v>
       </c>
       <c r="O9" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q9" s="11">
@@ -9408,7 +9592,7 @@
         <v>16</v>
       </c>
       <c r="S9" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9420,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="4">
-        <f t="shared" ref="C10:C20" si="4">ABS(A10-B10)</f>
+        <f t="shared" ref="C10:C20" si="5">ABS(A10-B10)</f>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="E10" s="11">
@@ -9430,7 +9614,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="4">
-        <f>ABS(E10-F10)</f>
+        <f t="shared" si="0"/>
         <v>1.021405182655144E-14</v>
       </c>
       <c r="H10" s="1"/>
@@ -9441,7 +9625,7 @@
         <v>8</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0198066269804258E-14</v>
       </c>
       <c r="L10" s="1"/>
@@ -9452,7 +9636,7 @@
         <v>203.25925925925901</v>
       </c>
       <c r="O10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q10" s="11">
@@ -9462,7 +9646,7 @@
         <v>32</v>
       </c>
       <c r="S10" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>107.93756174668599</v>
       </c>
     </row>
@@ -9474,7 +9658,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="E11" s="11">
@@ -9484,7 +9668,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="4">
-        <f>ABS(E11-F11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H11" s="1"/>
@@ -9495,7 +9679,7 @@
         <v>40</v>
       </c>
       <c r="K11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.9475983006414026E-14</v>
       </c>
       <c r="L11" s="1"/>
@@ -9506,7 +9690,7 @@
         <v>914.66666666666595</v>
       </c>
       <c r="O11" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0231815394945443E-12</v>
       </c>
       <c r="Q11" s="11">
@@ -9516,7 +9700,7 @@
         <v>1312</v>
       </c>
       <c r="S11" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>299.43805572021006</v>
       </c>
     </row>
@@ -9528,7 +9712,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E12" s="11">
@@ -9538,7 +9722,7 @@
         <v>16</v>
       </c>
       <c r="G12" s="4">
-        <f>ABS(E12-F12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H12" s="1"/>
@@ -9549,7 +9733,7 @@
         <v>200</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L12" s="1"/>
@@ -9560,7 +9744,7 @@
         <v>2845.62962962962</v>
       </c>
       <c r="O12" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q12" s="11">
@@ -9570,7 +9754,7 @@
         <v>38432</v>
       </c>
       <c r="S12" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9582,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E13" s="11">
@@ -9592,7 +9776,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="4">
-        <f>ABS(E13-F13)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H13" s="1"/>
@@ -9603,7 +9787,7 @@
         <v>36</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L13" s="1"/>
@@ -9614,7 +9798,7 @@
         <v>813.03703703703695</v>
       </c>
       <c r="O13" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q13" s="11">
@@ -9624,7 +9808,7 @@
         <v>1296</v>
       </c>
       <c r="S13" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9636,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D14" s="9"/>
@@ -9647,7 +9831,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="4">
-        <f>ABS(E14-F14)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14" s="2"/>
@@ -9658,7 +9842,7 @@
         <v>40</v>
       </c>
       <c r="K14" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.9475983006414026E-14</v>
       </c>
       <c r="L14" s="2"/>
@@ -9669,7 +9853,7 @@
         <v>914.66666666666595</v>
       </c>
       <c r="O14" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0231815394945443E-12</v>
       </c>
       <c r="P14" s="9"/>
@@ -9680,7 +9864,7 @@
         <v>1312</v>
       </c>
       <c r="S14" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>299.43805572021006</v>
       </c>
     </row>
@@ -9692,7 +9876,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="E15" s="11">
@@ -9702,7 +9886,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="4">
-        <f>ABS(E15-F15)</f>
+        <f t="shared" si="0"/>
         <v>9.9475983006414026E-14</v>
       </c>
       <c r="I15" s="11">
@@ -9712,7 +9896,7 @@
         <v>72</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.9475983006414026E-14</v>
       </c>
       <c r="M15" s="11">
@@ -9722,7 +9906,7 @@
         <v>1626.07407407407</v>
       </c>
       <c r="O15" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P15" s="9"/>
@@ -9733,7 +9917,7 @@
         <v>2592</v>
       </c>
       <c r="S15" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>534.18059672000982</v>
       </c>
     </row>
@@ -9745,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E16" s="11">
@@ -9755,7 +9939,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="4">
-        <f>ABS(E16-F16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I16" s="11">
@@ -9765,7 +9949,7 @@
         <v>232</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M16" s="11">
@@ -9775,7 +9959,7 @@
         <v>3557.0370370370301</v>
       </c>
       <c r="O16" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P16" s="9"/>
@@ -9786,7 +9970,7 @@
         <v>39712</v>
       </c>
       <c r="S16" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9798,7 +9982,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E17" s="11">
@@ -9808,7 +9992,7 @@
         <v>14</v>
       </c>
       <c r="G17" s="4">
-        <f>ABS(E17-F17)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I17" s="11">
@@ -9818,7 +10002,7 @@
         <v>196</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M17" s="11">
@@ -9828,7 +10012,7 @@
         <v>2744</v>
       </c>
       <c r="O17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P17" s="9"/>
@@ -9839,7 +10023,7 @@
         <v>38416</v>
       </c>
       <c r="S17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9851,7 +10035,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E18" s="11">
@@ -9861,7 +10045,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="4">
-        <f>ABS(E18-F18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I18" s="11">
@@ -9871,7 +10055,7 @@
         <v>200</v>
       </c>
       <c r="K18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M18" s="11">
@@ -9881,7 +10065,7 @@
         <v>2845.62962962962</v>
       </c>
       <c r="O18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P18" s="9"/>
@@ -9892,7 +10076,7 @@
         <v>38432</v>
       </c>
       <c r="S18" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9904,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E19" s="11">
@@ -9914,7 +10098,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="4">
-        <f>ABS(E19-F19)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I19" s="11">
@@ -9924,7 +10108,7 @@
         <v>232</v>
       </c>
       <c r="K19" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M19" s="11">
@@ -9934,7 +10118,7 @@
         <v>3557.0370370370301</v>
       </c>
       <c r="O19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P19" s="9"/>
@@ -9945,7 +10129,7 @@
         <v>39712</v>
       </c>
       <c r="S19" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -9957,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E20" s="11">
@@ -9967,7 +10151,7 @@
         <v>28</v>
       </c>
       <c r="G20" s="4">
-        <f>ABS(E20-F20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I20" s="11">
@@ -9977,7 +10161,7 @@
         <v>392</v>
       </c>
       <c r="K20" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M20" s="11">
@@ -9987,7 +10171,7 @@
         <v>5488</v>
       </c>
       <c r="O20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P20" s="9"/>
@@ -9998,7 +10182,7 @@
         <v>76832</v>
       </c>
       <c r="S20" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -10015,87 +10199,87 @@
       <c r="S22" s="3"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
       <c r="D23" s="9"/>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="15"/>
       <c r="L23" s="2"/>
-      <c r="M23" s="12" t="s">
+      <c r="M23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N23" s="13"/>
-      <c r="O23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="15"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="3"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="15"/>
       <c r="L24" s="2"/>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N24" s="13"/>
-      <c r="O24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="15"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="3"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
       <c r="D25" s="9"/>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="12" t="s">
+      <c r="I25" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J25" s="13"/>
-      <c r="K25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="15"/>
       <c r="L25" s="2"/>
-      <c r="M25" s="12" t="s">
+      <c r="M25" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="13"/>
-      <c r="O25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="15"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
@@ -10154,7 +10338,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="4">
-        <f>ABS(A27-B27)</f>
+        <f t="shared" ref="C27:C35" si="6">ABS(A27-B27)</f>
         <v>0</v>
       </c>
       <c r="D27" s="9"/>
@@ -10203,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="4">
-        <f>ABS(A28-B28)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D28" s="9"/>
@@ -10214,7 +10398,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" ref="G28:G42" si="5">ABS(E28-F28)</f>
+        <f t="shared" ref="G28:G42" si="7">ABS(E28-F28)</f>
         <v>0</v>
       </c>
       <c r="H28" s="2"/>
@@ -10225,7 +10409,7 @@
         <v>4</v>
       </c>
       <c r="K28" s="4">
-        <f t="shared" ref="K28:K42" si="6">ABS(I28-J28)</f>
+        <f t="shared" ref="K28:K42" si="8">ABS(I28-J28)</f>
         <v>0</v>
       </c>
       <c r="L28" s="2"/>
@@ -10236,7 +10420,7 @@
         <v>4</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" ref="O28:O42" si="7">ABS(M28-N28)</f>
+        <f t="shared" ref="O28:O42" si="9">ABS(M28-N28)</f>
         <v>0</v>
       </c>
       <c r="P28" s="9"/>
@@ -10252,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="4">
-        <f>ABS(A29-B29)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D29" s="9"/>
@@ -10263,7 +10447,7 @@
         <v>6</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H29" s="2"/>
@@ -10274,7 +10458,7 @@
         <v>36</v>
       </c>
       <c r="K29" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L29" s="2"/>
@@ -10285,7 +10469,7 @@
         <v>36</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P29" s="9"/>
@@ -10301,7 +10485,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="4">
-        <f>ABS(A30-B30)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D30" s="9"/>
@@ -10312,7 +10496,7 @@
         <v>14</v>
       </c>
       <c r="G30" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H30" s="2"/>
@@ -10323,7 +10507,7 @@
         <v>196</v>
       </c>
       <c r="K30" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L30" s="2"/>
@@ -10334,7 +10518,7 @@
         <v>196</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P30" s="9"/>
@@ -10350,7 +10534,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="4">
-        <f>ABS(A31-B31)</f>
+        <f t="shared" si="6"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D31" s="9"/>
@@ -10361,7 +10545,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H31" s="2"/>
@@ -10372,7 +10556,7 @@
         <v>4</v>
       </c>
       <c r="K31" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L31" s="2"/>
@@ -10383,7 +10567,7 @@
         <v>4</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P31" s="9"/>
@@ -10399,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="C32" s="4">
-        <f>ABS(A32-B32)</f>
+        <f t="shared" si="6"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D32" s="9"/>
@@ -10410,7 +10594,7 @@
         <v>4</v>
       </c>
       <c r="G32" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H32" s="2"/>
@@ -10421,7 +10605,7 @@
         <v>8</v>
       </c>
       <c r="K32" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>6.6492849669579357E-2</v>
       </c>
       <c r="L32" s="2"/>
@@ -10432,7 +10616,7 @@
         <v>8</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1.3064727540701426E-3</v>
       </c>
       <c r="P32" s="9"/>
@@ -10448,7 +10632,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="4">
-        <f>ABS(A33-B33)</f>
+        <f t="shared" si="6"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D33" s="9"/>
@@ -10459,7 +10643,7 @@
         <v>8</v>
       </c>
       <c r="G33" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H33" s="2"/>
@@ -10470,7 +10654,7 @@
         <v>40</v>
       </c>
       <c r="K33" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.1152231322024022</v>
       </c>
       <c r="L33" s="2"/>
@@ -10481,7 +10665,7 @@
         <v>40</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4.9452553458799287E-2</v>
       </c>
       <c r="P33" s="9"/>
@@ -10497,7 +10681,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="4">
-        <f>ABS(A34-B34)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D34" s="9"/>
@@ -10508,7 +10692,7 @@
         <v>16</v>
       </c>
       <c r="G34" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H34" s="2"/>
@@ -10519,7 +10703,7 @@
         <v>200</v>
       </c>
       <c r="K34" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>65.115223132202004</v>
       </c>
       <c r="L34" s="2"/>
@@ -10530,7 +10714,7 @@
         <v>200</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16.829168161492987</v>
       </c>
       <c r="P34" s="9"/>
@@ -10546,7 +10730,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="4">
-        <f>ABS(A35-B35)</f>
+        <f t="shared" si="6"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D35" s="9"/>
@@ -10557,7 +10741,7 @@
         <v>6</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H35" s="2"/>
@@ -10568,7 +10752,7 @@
         <v>36</v>
       </c>
       <c r="K35" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L35" s="2"/>
@@ -10579,7 +10763,7 @@
         <v>36</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P35" s="9"/>
@@ -10595,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="4">
-        <f t="shared" ref="C36:C42" si="8">ABS(A36-B36)</f>
+        <f t="shared" ref="C36:C42" si="10">ABS(A36-B36)</f>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D36" s="9"/>
@@ -10606,7 +10790,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H36" s="2"/>
@@ -10617,7 +10801,7 @@
         <v>40</v>
       </c>
       <c r="K36" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8.1648161849997791E-2</v>
       </c>
       <c r="L36" s="2"/>
@@ -10628,7 +10812,7 @@
         <v>40</v>
       </c>
       <c r="O36" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1.9927593989024217E-3</v>
       </c>
       <c r="P36" s="9"/>
@@ -10644,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9.9920072216264089E-16</v>
       </c>
       <c r="D37" s="9"/>
@@ -10655,7 +10839,7 @@
         <v>12</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9.9475983006414026E-14</v>
       </c>
       <c r="H37" s="2"/>
@@ -10666,7 +10850,7 @@
         <v>72</v>
       </c>
       <c r="K37" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.2527121243037982</v>
       </c>
       <c r="L37" s="2"/>
@@ -10677,7 +10861,7 @@
         <v>72</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6.3409128749896126E-2</v>
       </c>
       <c r="P37" s="9"/>
@@ -10693,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D38" s="9"/>
@@ -10704,7 +10888,7 @@
         <v>20</v>
       </c>
       <c r="G38" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H38" s="2"/>
@@ -10715,7 +10899,7 @@
         <v>232</v>
       </c>
       <c r="K38" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>65.252712124303002</v>
       </c>
       <c r="L38" s="2"/>
@@ -10726,7 +10910,7 @@
         <v>232</v>
       </c>
       <c r="O38" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16.939234532343988</v>
       </c>
       <c r="P38" s="9"/>
@@ -10742,7 +10926,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D39" s="9"/>
@@ -10753,7 +10937,7 @@
         <v>14</v>
       </c>
       <c r="G39" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H39" s="2"/>
@@ -10764,7 +10948,7 @@
         <v>196</v>
       </c>
       <c r="K39" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L39" s="2"/>
@@ -10775,7 +10959,7 @@
         <v>196</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P39" s="9"/>
@@ -10791,7 +10975,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D40" s="9"/>
@@ -10802,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="G40" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H40" s="2"/>
@@ -10813,7 +10997,7 @@
         <v>200</v>
       </c>
       <c r="K40" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L40" s="2"/>
@@ -10824,7 +11008,7 @@
         <v>200</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P40" s="9"/>
@@ -10840,7 +11024,7 @@
         <v>1</v>
       </c>
       <c r="C41" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D41" s="9"/>
@@ -10851,7 +11035,7 @@
         <v>20</v>
       </c>
       <c r="G41" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H41" s="2"/>
@@ -10862,7 +11046,7 @@
         <v>232</v>
       </c>
       <c r="K41" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L41" s="2"/>
@@ -10873,7 +11057,7 @@
         <v>232</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P41" s="9"/>
@@ -10889,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D42" s="9"/>
@@ -10900,7 +11084,7 @@
         <v>28</v>
       </c>
       <c r="G42" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H42" s="2"/>
@@ -10911,7 +11095,7 @@
         <v>392</v>
       </c>
       <c r="K42" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L42" s="2"/>
@@ -10922,7 +11106,7 @@
         <v>392</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P42" s="9"/>
@@ -10932,6 +11116,25 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="Q3:S3"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="I24:K24"/>
@@ -10940,25 +11143,6 @@
     <mergeCell ref="E25:G25"/>
     <mergeCell ref="I25:K25"/>
     <mergeCell ref="M25:O25"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
